--- a/docs/testing/metadonnees/Template - Tests in metadata workbook.xlsx
+++ b/docs/testing/metadonnees/Template - Tests in metadata workbook.xlsx
@@ -7,13 +7,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F17-Surgery Admission" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Scenarios" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User flow template" sheetId="2" state="hidden" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form QA Tracker" sheetId="3" state="hidden" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form Guidance" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'F17-Surgery Admission'!$A$2:$BR$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Scenarios'!$A$2:$G$500</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'F17-Surgery Admission'!$A$2:$BP$17</definedName>
   </definedNames>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,7 +25,7 @@
     <numFmt numFmtId="165" formatCode="[$-2000401]0"/>
     <numFmt numFmtId="166" formatCode="[$-2000000]\d\d\-mmm"/>
   </numFmts>
-  <fonts count="130">
+  <fonts count="129">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -877,11 +876,6 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FF2E75B6"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
       <i val="1"/>
       <color rgb="FF2E75B6"/>
     </font>
@@ -890,7 +884,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="64">
+  <fills count="63">
     <fill>
       <patternFill/>
     </fill>
@@ -1261,11 +1255,6 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2E75B6"/>
       </patternFill>
     </fill>
   </fills>
@@ -2112,7 +2101,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="804">
+  <cellXfs count="801">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3710,14 +3699,9 @@
     <xf numFmtId="0" fontId="90" fillId="52" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="127" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="63" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="128" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="127" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="129" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="128" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="4">
@@ -8329,9 +8313,9 @@
     <author>LIME</author>
   </authors>
   <commentList>
-    <comment ref="BQ2" authorId="0" shapeId="0">
+    <comment ref="BK2" authorId="0" shapeId="0">
       <text>
-        <t>Optional. One test per row, written as 'If I do... / I should see...'. Skip logic, Mandatory and Lower/Upper limit are already turned into tests automatically: no need to repeat them here.</t>
+        <t>Tests on this question go here, one per line: 'Test: &lt;what I do&gt; -&gt; &lt;what I should see&gt;'. Skip logic, Mandatory and limits already become tests automatically.</t>
       </text>
     </comment>
   </commentList>
@@ -8344,14 +8328,29 @@
     <author>LIME</author>
   </authors>
   <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Step = form code + step number (F17-1, F17-2...). Action = what I do. Description = what I should see. One scenario = the steps sharing the same prefix.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>LIME</author>
+  </authors>
+  <commentList>
     <comment ref="B8" authorId="0" shapeId="0">
       <text>
-        <t>Filled from scripts/metadata-check.py --all (mandatory, limits, questions present).</t>
+        <t>From scripts/metadata-check.py --all: questions present, mandatory, limits.</t>
       </text>
     </comment>
     <comment ref="D8" authorId="0" shapeId="0">
       <text>
-        <t>Filled from scripts/metadata-check.py --all (every Skip logic rule, both ways).</t>
+        <t>From scripts/metadata-check.py --all: every Skip logic rule, both ways.</t>
       </text>
     </comment>
   </commentList>
@@ -9145,7 +9144,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR17"/>
+  <dimension ref="A1:BP17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col outlineLevel="1" width="21.42578125" customWidth="1" min="1" max="1"/>
@@ -9191,10 +9190,8 @@
     <col width="48.42578125" customWidth="1" min="62" max="62"/>
     <col width="45" customWidth="1" min="63" max="63"/>
     <col width="18.5703125" customWidth="1" min="64" max="64"/>
-    <col hidden="1" width="13" customWidth="1" min="66" max="67"/>
+    <col hidden="1" min="66" max="67"/>
     <col width="21.42578125" customWidth="1" min="68" max="68"/>
-    <col width="42" customWidth="1" min="69" max="69"/>
-    <col width="42" customWidth="1" min="70" max="70"/>
   </cols>
   <sheetData>
     <row r="1" ht="22.35" customHeight="1">
@@ -9249,11 +9246,6 @@
           <t>F17-Surgery admission form</t>
         </is>
       </c>
-      <c r="BQ1" s="799" t="inlineStr">
-        <is>
-          <t>NEW (optional): only for what the columns above cannot express</t>
-        </is>
-      </c>
     </row>
     <row r="2" ht="30" customFormat="1" customHeight="1" s="1">
       <c r="A2" s="2" t="inlineStr">
@@ -9594,16 +9586,6 @@
       <c r="BP2" s="2" t="inlineStr">
         <is>
           <t>Question ID</t>
-        </is>
-      </c>
-      <c r="BQ2" s="800" t="inlineStr">
-        <is>
-          <t>Test - If I do...</t>
-        </is>
-      </c>
-      <c r="BR2" s="800" t="inlineStr">
-        <is>
-          <t>Test - I should see...</t>
         </is>
       </c>
     </row>
@@ -9725,6 +9707,7 @@
           <t>تاريخ الدخول</t>
         </is>
       </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
           <t>بيانات القبول</t>
@@ -9898,6 +9881,7 @@
       <c r="BO4" s="41" t="n">
         <v>4</v>
       </c>
+      <c r="BP4" t="inlineStr"/>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
@@ -10008,6 +9992,7 @@
       <c r="BO5" s="41" t="n">
         <v>4</v>
       </c>
+      <c r="BP5" t="inlineStr"/>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
@@ -10128,6 +10113,7 @@
           <t>نوع الدخول</t>
         </is>
       </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
           <t>بيانات القبول</t>
@@ -10309,6 +10295,7 @@
           <t>تمت إحالته إلى منظمة أطباء بلا حدود</t>
         </is>
       </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
           <t>بيانات القبول</t>
@@ -10494,6 +10481,7 @@
           <t>مُشار إليه - من قبل من / من أين</t>
         </is>
       </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
           <t>بيانات القبول</t>
@@ -10678,6 +10666,7 @@
           <t>إذا كان غير ذلك، حدد</t>
         </is>
       </c>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
           <t>بيانات القبول</t>
@@ -10864,6 +10853,7 @@
           <t>المريض القادم من</t>
         </is>
       </c>
+      <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
           <t>بيانات القبول</t>
@@ -11048,6 +11038,7 @@
           <t>إذا كان غير ذلك، حدد</t>
         </is>
       </c>
+      <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
           <t>بيانات القبول</t>
@@ -11220,6 +11211,7 @@
           <t>الوقت منذ ظهور الأعراض/الإصابة حتى الدخول إلى المستشفى (بالساعات)</t>
         </is>
       </c>
+      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
           <t>تفاصيل القبول</t>
@@ -11397,6 +11389,7 @@
       <c r="BO13" s="41" t="n">
         <v>4</v>
       </c>
+      <c r="BP13" t="inlineStr"/>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
@@ -11573,7 +11566,11 @@
       </c>
       <c r="BI14" s="665" t="n"/>
       <c r="BJ14" s="665" t="n"/>
-      <c r="BK14" s="32" t="n"/>
+      <c r="BK14" s="799" t="inlineStr">
+        <is>
+          <t>Test: Enter 450 -&gt; A warning: the weight is not plausible</t>
+        </is>
+      </c>
       <c r="BN14" t="inlineStr">
         <is>
           <t>F17-Surgery admission form|9e3c4083-21bd-42d4-a2b5-657bc0b8a4a5</t>
@@ -11585,16 +11582,6 @@
       <c r="BP14" t="inlineStr">
         <is>
           <t>rfe-forms-weightAtAdmission</t>
-        </is>
-      </c>
-      <c r="BQ14" s="801" t="inlineStr">
-        <is>
-          <t>Enter 450</t>
-        </is>
-      </c>
-      <c r="BR14" s="801" t="inlineStr">
-        <is>
-          <t>A warning or refusal: the weight is not plausible</t>
         </is>
       </c>
     </row>
@@ -11706,6 +11693,7 @@
           <t>التعليقات</t>
         </is>
       </c>
+      <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
           <t>تفاصيل القبول</t>
@@ -11866,6 +11854,7 @@
           <t>وصف الفحوصات والأدوية الجديدة من سلة الطلبات عند الضرورة (بعد إغلاق هذا النموذج)</t>
         </is>
       </c>
+      <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
           <t>تفاصيل القبول</t>
@@ -12030,6 +12019,7 @@
           <t>طلب الأدوية</t>
         </is>
       </c>
+      <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
           <t>تفاصيل القبول</t>
@@ -12077,7 +12067,11 @@
       </c>
       <c r="BI17" s="665" t="n"/>
       <c r="BJ17" s="670" t="n"/>
-      <c r="BK17" s="32" t="n"/>
+      <c r="BK17" s="799" t="inlineStr">
+        <is>
+          <t>Test: Click « Order medications » -&gt; The order basket opens for this patient</t>
+        </is>
+      </c>
       <c r="BN17" t="inlineStr">
         <is>
           <t>F17-Surgery admission form|WORKSPACE</t>
@@ -12089,22 +12083,12 @@
       <c r="BP17" s="57" t="inlineStr">
         <is>
           <t>rfe-forms-orderMedications</t>
-        </is>
-      </c>
-      <c r="BQ17" s="801" t="inlineStr">
-        <is>
-          <t>Click « Order medications »</t>
-        </is>
-      </c>
-      <c r="BR17" s="801" t="inlineStr">
-        <is>
-          <t>The order basket opens for this patient</t>
         </is>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
-  <autoFilter ref="A2:BR17"/>
+  <autoFilter ref="A2:BP17"/>
   <mergeCells count="5">
     <mergeCell ref="BA1:BF1"/>
     <mergeCell ref="S1:X1"/>
@@ -12141,170 +12125,160 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Sheet24">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="14.45"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="4"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="7"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="802" t="inlineStr">
-        <is>
-          <t>Tests that are not about a single question: patient journeys, several forms, roles and access, reports. One row per test.</t>
+    <row r="1" ht="26.25" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Permission</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Comment</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Form</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Who (role, site)</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>If I do...</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>I should see...</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Comments</t>
+      <c r="A2" s="799" t="inlineStr">
+        <is>
+          <t>F17-1</t>
+        </is>
+      </c>
+      <c r="B2" s="799" t="inlineStr">
+        <is>
+          <t>Save a Surgery Admission form for a patient with an active visit</t>
+        </is>
+      </c>
+      <c r="C2" s="799" t="inlineStr">
+        <is>
+          <t>The admission appears in the visit with its admission date</t>
+        </is>
+      </c>
+      <c r="D2" s="799" t="inlineStr">
+        <is>
+          <t>Fictitious patient, active visit</t>
+        </is>
+      </c>
+      <c r="E2" s="799" t="inlineStr">
+        <is>
+          <t>Surgeon, Mosul</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="801" t="inlineStr">
-        <is>
-          <t>F17-Surgery Admission</t>
-        </is>
-      </c>
-      <c r="B3" s="801" t="inlineStr">
+      <c r="A3" s="799" t="inlineStr">
+        <is>
+          <t>F17-2</t>
+        </is>
+      </c>
+      <c r="B3" s="799" t="inlineStr">
+        <is>
+          <t>Open Surgery Discharge (F18) for the same patient</t>
+        </is>
+      </c>
+      <c r="C3" s="799" t="inlineStr">
+        <is>
+          <t>The admission date is shown in the discharge form</t>
+        </is>
+      </c>
+      <c r="E3" s="799" t="inlineStr">
         <is>
           <t>Surgeon, Mosul</t>
-        </is>
-      </c>
-      <c r="C3" s="801" t="inlineStr">
-        <is>
-          <t>Save a Surgery Admission form, then open the patient chart</t>
-        </is>
-      </c>
-      <c r="D3" s="801" t="inlineStr">
-        <is>
-          <t>The admission appears in the visit with its admission date</t>
-        </is>
-      </c>
-      <c r="E3" s="801" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="F3" s="801" t="inlineStr">
-        <is>
-          <t>Example</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="801" t="inlineStr">
-        <is>
-          <t>F35-MH-PHQ-9</t>
-        </is>
-      </c>
-      <c r="B4" s="801" t="inlineStr">
+      <c r="A4" s="799" t="inlineStr">
+        <is>
+          <t>F35-1</t>
+        </is>
+      </c>
+      <c r="B4" s="799" t="inlineStr">
+        <is>
+          <t>Answer « Nearly every day (3 points) » to the 9 PHQ-9 questions</t>
+        </is>
+      </c>
+      <c r="C4" s="799" t="inlineStr">
+        <is>
+          <t>PHQ-9 score = 27</t>
+        </is>
+      </c>
+      <c r="E4" s="799" t="inlineStr">
         <is>
           <t>Mental health clinician, all sites</t>
-        </is>
-      </c>
-      <c r="C4" s="801" t="inlineStr">
-        <is>
-          <t>Answer « Nearly every day (3 points) » to the 9 questions</t>
-        </is>
-      </c>
-      <c r="D4" s="801" t="inlineStr">
-        <is>
-          <t>PHQ-9 score = 27</t>
-        </is>
-      </c>
-      <c r="E4" s="801" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="F4" s="801" t="inlineStr">
-        <is>
-          <t>Example</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="801" t="inlineStr">
-        <is>
-          <t>(Roles)</t>
-        </is>
-      </c>
-      <c r="B5" s="801" t="inlineStr">
-        <is>
-          <t>Matsapha, « Clinical » role</t>
-        </is>
-      </c>
-      <c r="C5" s="801" t="inlineStr">
+      <c r="A5" s="799" t="inlineStr">
+        <is>
+          <t>ROLES-1</t>
+        </is>
+      </c>
+      <c r="B5" s="799" t="inlineStr">
         <is>
           <t>Open a patient chart</t>
         </is>
       </c>
-      <c r="D5" s="801" t="inlineStr">
+      <c r="C5" s="799" t="inlineStr">
         <is>
           <t>No « Delete » button for visits or encounters</t>
         </is>
       </c>
-      <c r="E5" s="801" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="F5" s="801" t="inlineStr">
-        <is>
-          <t>Example</t>
+      <c r="E5" s="799" t="inlineStr">
+        <is>
+          <t>Matsapha « Clinical » role</t>
+        </is>
+      </c>
+      <c r="F5" s="799" t="inlineStr">
+        <is>
+          <t>No Delete privileges</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:G500"/>
-  <dataValidations count="1">
-    <dataValidation sqref="E3:E500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Critical,Normal"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -12597,26 +12571,21 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="803" t="inlineStr">
+      <c r="A8" s="799" t="inlineStr">
         <is>
           <t>F17-Surgery Admission</t>
         </is>
       </c>
-      <c r="B8" s="803" t="inlineStr">
+      <c r="B8" s="799" t="inlineStr">
         <is>
           <t>Auto, Oct 13: ✅ 2/2</t>
         </is>
       </c>
-      <c r="C8" s="803" t="n"/>
-      <c r="D8" s="803" t="inlineStr">
+      <c r="D8" s="799" t="inlineStr">
         <is>
           <t>Auto, Oct 13: ✅ 8/8</t>
         </is>
       </c>
-      <c r="E8" s="803" t="n"/>
-      <c r="F8" s="803" t="n"/>
-      <c r="G8" s="803" t="n"/>
-      <c r="H8" s="803" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12978,25 +12947,24 @@
       <c r="D28" s="238" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="802" t="inlineStr">
+      <c r="A30" s="800" t="inlineStr">
         <is>
           <t>Tests</t>
         </is>
       </c>
-      <c r="B30" s="612" t="inlineStr">
-        <is>
-          <t>Skip logic, Mandatory and Lower/Upper limit are turned into tests automatically. Use the 'Test - If I do...' / 'Test - I should see...' columns only for other rules of a question (calculations, plausibility, buttons), and the 'Test Scenarios' tab for tests across questions or forms. Write the expected result precisely ('score = 27', not 'works').</t>
-        </is>
-      </c>
-      <c r="C30" s="612" t="inlineStr">
-        <is>
-          <t>If I do: Enter 450 in 'Weight at admission (in kg)'
-I should see: a warning, the weight is not plausible</t>
-        </is>
-      </c>
-      <c r="D30" s="612" t="inlineStr">
-        <is>
-          <t>I should see: it works</t>
+      <c r="B30" s="799" t="inlineStr">
+        <is>
+          <t>Skip logic, Mandatory and Lower/Upper limit become tests automatically. Other tests on a question: in 'Comments', one per line, 'Test: &lt;what I do&gt; -&gt; &lt;what I should see&gt;'. Tests across questions or forms: 'User flow template' tab (Action = what I do, Description = what I should see).</t>
+        </is>
+      </c>
+      <c r="C30" s="799" t="inlineStr">
+        <is>
+          <t>Test: Enter 450 -&gt; A warning: the weight is not plausible</t>
+        </is>
+      </c>
+      <c r="D30" s="799" t="inlineStr">
+        <is>
+          <t>Test: weight works</t>
         </is>
       </c>
     </row>

--- a/docs/testing/metadonnees/Template - Tests in metadata workbook.xlsx
+++ b/docs/testing/metadonnees/Template - Tests in metadata workbook.xlsx
@@ -9190,7 +9190,7 @@
     <col width="48.42578125" customWidth="1" min="62" max="62"/>
     <col width="45" customWidth="1" min="63" max="63"/>
     <col width="18.5703125" customWidth="1" min="64" max="64"/>
-    <col hidden="1" min="66" max="67"/>
+    <col hidden="1" width="13" customWidth="1" min="66" max="67"/>
     <col width="21.42578125" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
@@ -9707,7 +9707,6 @@
           <t>تاريخ الدخول</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
           <t>بيانات القبول</t>
@@ -9881,7 +9880,6 @@
       <c r="BO4" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="BP4" t="inlineStr"/>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
@@ -9992,7 +9990,6 @@
       <c r="BO5" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="BP5" t="inlineStr"/>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
@@ -10113,7 +10110,6 @@
           <t>نوع الدخول</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
           <t>بيانات القبول</t>
@@ -10295,7 +10291,6 @@
           <t>تمت إحالته إلى منظمة أطباء بلا حدود</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
           <t>بيانات القبول</t>
@@ -10481,7 +10476,6 @@
           <t>مُشار إليه - من قبل من / من أين</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
           <t>بيانات القبول</t>
@@ -10666,7 +10660,6 @@
           <t>إذا كان غير ذلك، حدد</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
           <t>بيانات القبول</t>
@@ -10853,7 +10846,6 @@
           <t>المريض القادم من</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
           <t>بيانات القبول</t>
@@ -11038,7 +11030,6 @@
           <t>إذا كان غير ذلك، حدد</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
           <t>بيانات القبول</t>
@@ -11211,7 +11202,6 @@
           <t>الوقت منذ ظهور الأعراض/الإصابة حتى الدخول إلى المستشفى (بالساعات)</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
           <t>تفاصيل القبول</t>
@@ -11389,7 +11379,6 @@
       <c r="BO13" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="BP13" t="inlineStr"/>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
@@ -11693,7 +11682,6 @@
           <t>التعليقات</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
           <t>تفاصيل القبول</t>
@@ -11854,7 +11842,6 @@
           <t>وصف الفحوصات والأدوية الجديدة من سلة الطلبات عند الضرورة (بعد إغلاق هذا النموذج)</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
           <t>تفاصيل القبول</t>
@@ -12019,7 +12006,6 @@
           <t>طلب الأدوية</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
           <t>تفاصيل القبول</t>
@@ -12129,7 +12115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="14.45"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12273,6 +12259,50 @@
       <c r="F5" s="799" t="inlineStr">
         <is>
           <t>No Delete privileges</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="799" t="inlineStr">
+        <is>
+          <t>DHIS2-1</t>
+        </is>
+      </c>
+      <c r="B6" s="799" t="inlineStr">
+        <is>
+          <t>Save an F17 form, wait for the nightly sync</t>
+        </is>
+      </c>
+      <c r="C6" s="799" t="inlineStr">
+        <is>
+          <t>The admission appears in DHIS2 with the right date</t>
+        </is>
+      </c>
+      <c r="E6" s="799" t="inlineStr">
+        <is>
+          <t>Data officer</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="799" t="inlineStr">
+        <is>
+          <t>REPORT-1</t>
+        </is>
+      </c>
+      <c r="B7" s="799" t="inlineStr">
+        <is>
+          <t>Run the monthly mental health report for September</t>
+        </is>
+      </c>
+      <c r="C7" s="799" t="inlineStr">
+        <is>
+          <t>The number of new patients matches the patient list</t>
+        </is>
+      </c>
+      <c r="E7" s="799" t="inlineStr">
+        <is>
+          <t>MH manager</t>
         </is>
       </c>
     </row>

--- a/docs/testing/metadonnees/Template - Tests in metadata workbook.xlsx
+++ b/docs/testing/metadonnees/Template - Tests in metadata workbook.xlsx
@@ -12115,7 +12115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="14.45"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12123,8 +12123,8 @@
     <col width="50" customWidth="1" min="3" max="4"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="7"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="6" max="7"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26.25" customHeight="1">
@@ -12187,7 +12187,7 @@
       </c>
       <c r="E2" s="799" t="inlineStr">
         <is>
-          <t>Surgeon, Mosul</t>
+          <t>Surgeon</t>
         </is>
       </c>
     </row>
@@ -12209,7 +12209,7 @@
       </c>
       <c r="E3" s="799" t="inlineStr">
         <is>
-          <t>Surgeon, Mosul</t>
+          <t>Surgeon</t>
         </is>
       </c>
     </row>
@@ -12231,7 +12231,7 @@
       </c>
       <c r="E4" s="799" t="inlineStr">
         <is>
-          <t>Mental health clinician, all sites</t>
+          <t>MH psychologist</t>
         </is>
       </c>
     </row>
@@ -12243,64 +12243,273 @@
       </c>
       <c r="B5" s="799" t="inlineStr">
         <is>
-          <t>Open a patient chart</t>
+          <t>Register a new patient, then open their patient file</t>
         </is>
       </c>
       <c r="C5" s="799" t="inlineStr">
         <is>
-          <t>No « Delete » button for visits or encounters</t>
+          <t>Registration works; the patient file (clinical tabs) is not accessible</t>
         </is>
       </c>
       <c r="E5" s="799" t="inlineStr">
         <is>
-          <t>Matsapha « Clinical » role</t>
+          <t>Registration Clerk</t>
         </is>
       </c>
       <c r="F5" s="799" t="inlineStr">
         <is>
-          <t>No Delete privileges</t>
+          <t>Patients &gt; Create: x; See patient file: blank</t>
+        </is>
+      </c>
+      <c r="G5" s="799" t="inlineStr">
+        <is>
+          <t>From the User roles and privileges tab</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="799" t="inlineStr">
         <is>
-          <t>DHIS2-1</t>
+          <t>ROLES-2</t>
         </is>
       </c>
       <c r="B6" s="799" t="inlineStr">
         <is>
-          <t>Save an F17 form, wait for the nightly sync</t>
+          <t>Open a patient file and try to order a lab test</t>
         </is>
       </c>
       <c r="C6" s="799" t="inlineStr">
         <is>
-          <t>The admission appears in DHIS2 with the right date</t>
+          <t>No lab order option</t>
         </is>
       </c>
       <c r="E6" s="799" t="inlineStr">
         <is>
-          <t>Data officer</t>
+          <t>MH counselor</t>
+        </is>
+      </c>
+      <c r="F6" s="799" t="inlineStr">
+        <is>
+          <t>Lab &gt; Order lab test: blank</t>
+        </is>
+      </c>
+      <c r="G6" s="799" t="inlineStr">
+        <is>
+          <t>From the User roles and privileges tab</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="799" t="inlineStr">
         <is>
+          <t>ROLES-3</t>
+        </is>
+      </c>
+      <c r="B7" s="799" t="inlineStr">
+        <is>
+          <t>Open a patient file, go to Vitals</t>
+        </is>
+      </c>
+      <c r="C7" s="799" t="inlineStr">
+        <is>
+          <t>Vitals are visible, no « Add » button</t>
+        </is>
+      </c>
+      <c r="E7" s="799" t="inlineStr">
+        <is>
+          <t>MedCo</t>
+        </is>
+      </c>
+      <c r="F7" s="799" t="inlineStr">
+        <is>
+          <t>Vitals &gt; View: x; Add: blank</t>
+        </is>
+      </c>
+      <c r="G7" s="799" t="inlineStr">
+        <is>
+          <t>From the User roles and privileges tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="799" t="inlineStr">
+        <is>
+          <t>ROLES-4</t>
+        </is>
+      </c>
+      <c r="B8" s="799" t="inlineStr">
+        <is>
+          <t>Open a past visit and try to edit it</t>
+        </is>
+      </c>
+      <c r="C8" s="799" t="inlineStr">
+        <is>
+          <t>Editing is refused</t>
+        </is>
+      </c>
+      <c r="E8" s="799" t="inlineStr">
+        <is>
+          <t>MH psychologist</t>
+        </is>
+      </c>
+      <c r="F8" s="799" t="inlineStr">
+        <is>
+          <t>Visits &gt; Edit: blank</t>
+        </is>
+      </c>
+      <c r="G8" s="799" t="inlineStr">
+        <is>
+          <t>From the User roles and privileges tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="799" t="inlineStr">
+        <is>
+          <t>REG-1</t>
+        </is>
+      </c>
+      <c r="B9" s="799" t="inlineStr">
+        <is>
+          <t>Register a new patient</t>
+        </is>
+      </c>
+      <c r="C9" s="799" t="inlineStr">
+        <is>
+          <t>An MSF ID is generated with the prefix IQ146- and at most 16 characters</t>
+        </is>
+      </c>
+      <c r="E9" s="799" t="inlineStr">
+        <is>
+          <t>Registration Clerk</t>
+        </is>
+      </c>
+      <c r="G9" s="799" t="inlineStr">
+        <is>
+          <t>From the Patient Identifiers tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="799" t="inlineStr">
+        <is>
+          <t>PRINT-1</t>
+        </is>
+      </c>
+      <c r="B10" s="799" t="inlineStr">
+        <is>
+          <t>Print the patient sticker</t>
+        </is>
+      </c>
+      <c r="C10" s="799" t="inlineStr">
+        <is>
+          <t>Shows Patient ID, first and last name, gender and date of birth, in Arabic</t>
+        </is>
+      </c>
+      <c r="E10" s="799" t="inlineStr">
+        <is>
+          <t>Registration Clerk</t>
+        </is>
+      </c>
+      <c r="G10" s="799" t="inlineStr">
+        <is>
+          <t>From the Patient Sticker tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="799" t="inlineStr">
+        <is>
+          <t>APPT-1</t>
+        </is>
+      </c>
+      <c r="B11" s="799" t="inlineStr">
+        <is>
+          <t>Book an appointment for a patient</t>
+        </is>
+      </c>
+      <c r="C11" s="799" t="inlineStr">
+        <is>
+          <t>Services offered: General Medicine, Outpatient Department, Rehabilitation, Mental Health</t>
+        </is>
+      </c>
+      <c r="E11" s="799" t="inlineStr">
+        <is>
+          <t>MH psychologist</t>
+        </is>
+      </c>
+      <c r="G11" s="799" t="inlineStr">
+        <is>
+          <t>From the Appointment Service Definitions tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="799" t="inlineStr">
+        <is>
+          <t>VISIT-1</t>
+        </is>
+      </c>
+      <c r="B12" s="799" t="inlineStr">
+        <is>
+          <t>Start a visit</t>
+        </is>
+      </c>
+      <c r="C12" s="799" t="inlineStr">
+        <is>
+          <t>Visit types offered: Facility Visit, Home Visit, OPD Visit, Offline Visit, Group Session</t>
+        </is>
+      </c>
+      <c r="E12" s="799" t="inlineStr">
+        <is>
+          <t>MH psychologist</t>
+        </is>
+      </c>
+      <c r="G12" s="799" t="inlineStr">
+        <is>
+          <t>From the Visit Types tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="799" t="inlineStr">
+        <is>
+          <t>DHIS2-1</t>
+        </is>
+      </c>
+      <c r="B13" s="799" t="inlineStr">
+        <is>
+          <t>Save an F17 form, wait for the next DHIS2 sync</t>
+        </is>
+      </c>
+      <c r="C13" s="799" t="inlineStr">
+        <is>
+          <t>The admission appears in DHIS2 with the right date</t>
+        </is>
+      </c>
+      <c r="E13" s="799" t="inlineStr">
+        <is>
+          <t>Data officer</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="799" t="inlineStr">
+        <is>
           <t>REPORT-1</t>
         </is>
       </c>
-      <c r="B7" s="799" t="inlineStr">
-        <is>
-          <t>Run the monthly mental health report for September</t>
-        </is>
-      </c>
-      <c r="C7" s="799" t="inlineStr">
+      <c r="B14" s="799" t="inlineStr">
+        <is>
+          <t>Run the monthly mental health report for last month</t>
+        </is>
+      </c>
+      <c r="C14" s="799" t="inlineStr">
         <is>
           <t>The number of new patients matches the patient list</t>
         </is>
       </c>
-      <c r="E7" s="799" t="inlineStr">
+      <c r="E14" s="799" t="inlineStr">
         <is>
           <t>MH manager</t>
         </is>

--- a/docs/testing/metadonnees/Template - Tests in metadata workbook.xlsx
+++ b/docs/testing/metadonnees/Template - Tests in metadata workbook.xlsx
@@ -12430,7 +12430,7 @@
       </c>
       <c r="C11" s="799" t="inlineStr">
         <is>
-          <t>Services offered: General Medicine, Outpatient Department, Rehabilitation, Mental Health</t>
+          <t>Services offered: Mental Health, and the Mental Health sub-services (AB, DT, KA, SA, SK)</t>
         </is>
       </c>
       <c r="E11" s="799" t="inlineStr">
@@ -12440,7 +12440,7 @@
       </c>
       <c r="G11" s="799" t="inlineStr">
         <is>
-          <t>From the Appointment Service Definitions tab</t>
+          <t>Appointment Service Definitions tab is out of date (lists General Medicine, OPD, Rehabilitation): update it first</t>
         </is>
       </c>
     </row>
@@ -12457,7 +12457,7 @@
       </c>
       <c r="C12" s="799" t="inlineStr">
         <is>
-          <t>Visit types offered: Facility Visit, Home Visit, OPD Visit, Offline Visit, Group Session</t>
+          <t>Visit types offered: OPD Visit, ER Visit, IPD Visit, Telehealth</t>
         </is>
       </c>
       <c r="E12" s="799" t="inlineStr">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="G12" s="799" t="inlineStr">
         <is>
-          <t>From the Visit Types tab</t>
+          <t>Visit Types tab is out of date (lists Facility, Home, Offline, Group Session visits): update it first</t>
         </is>
       </c>
     </row>

--- a/docs/testing/metadonnees/Template - Tests in metadata workbook.xlsx
+++ b/docs/testing/metadonnees/Template - Tests in metadata workbook.xlsx
@@ -11557,7 +11557,7 @@
       <c r="BJ14" s="665" t="n"/>
       <c r="BK14" s="799" t="inlineStr">
         <is>
-          <t>Test: Enter 450 -&gt; A warning: the weight is not plausible</t>
+          <t>Test: Enter 450 -&gt; The value is refused (needs an Upper limit)</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -12167,17 +12167,17 @@
     <row r="2">
       <c r="A2" s="799" t="inlineStr">
         <is>
-          <t>F17-1</t>
+          <t>F31-1</t>
         </is>
       </c>
       <c r="B2" s="799" t="inlineStr">
         <is>
-          <t>Save a Surgery Admission form for a patient with an active visit</t>
+          <t>Save an F31 mhGAP Baseline during an active visit, then open the patient chart</t>
         </is>
       </c>
       <c r="C2" s="799" t="inlineStr">
         <is>
-          <t>The admission appears in the visit with its admission date</t>
+          <t>The form appears under the visit in the Visits tab and in Forms &amp; Notes</t>
         </is>
       </c>
       <c r="D2" s="799" t="inlineStr">
@@ -12187,95 +12187,105 @@
       </c>
       <c r="E2" s="799" t="inlineStr">
         <is>
-          <t>Surgeon</t>
+          <t>Mental Health Counselor (MH counselor)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="799" t="inlineStr">
         <is>
-          <t>F17-2</t>
+          <t>F35-1</t>
         </is>
       </c>
       <c r="B3" s="799" t="inlineStr">
         <is>
-          <t>Open Surgery Discharge (F18) for the same patient</t>
+          <t>Answer « Nearly every day (3 points) » to the 9 PHQ-9 questions</t>
         </is>
       </c>
       <c r="C3" s="799" t="inlineStr">
         <is>
-          <t>The admission date is shown in the discharge form</t>
+          <t>PHQ-9 score = 27</t>
         </is>
       </c>
       <c r="E3" s="799" t="inlineStr">
         <is>
-          <t>Surgeon</t>
+          <t>Mental Health Counselor (MH counselor)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="799" t="inlineStr">
         <is>
-          <t>F35-1</t>
+          <t>ROLES-1</t>
         </is>
       </c>
       <c r="B4" s="799" t="inlineStr">
         <is>
-          <t>Answer « Nearly every day (3 points) » to the 9 PHQ-9 questions</t>
+          <t>Open the patient chart of a mental health patient</t>
         </is>
       </c>
       <c r="C4" s="799" t="inlineStr">
         <is>
-          <t>PHQ-9 score = 27</t>
+          <t>Mental health forms are not visible</t>
         </is>
       </c>
       <c r="E4" s="799" t="inlineStr">
         <is>
-          <t>MH psychologist</t>
+          <t>Registration Officer (Registration Clerk)</t>
+        </is>
+      </c>
+      <c r="F4" s="799" t="inlineStr">
+        <is>
+          <t>No « View Mental Health »</t>
+        </is>
+      </c>
+      <c r="G4" s="799" t="inlineStr">
+        <is>
+          <t>Today: config matches</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="799" t="inlineStr">
         <is>
-          <t>ROLES-1</t>
+          <t>ROLES-2</t>
         </is>
       </c>
       <c r="B5" s="799" t="inlineStr">
         <is>
-          <t>Register a new patient, then open their patient file</t>
+          <t>Open an F31 mhGAP Baseline, go to Clinical diagnosis</t>
         </is>
       </c>
       <c r="C5" s="799" t="inlineStr">
         <is>
-          <t>Registration works; the patient file (clinical tabs) is not accessible</t>
+          <t>The section is read-only</t>
         </is>
       </c>
       <c r="E5" s="799" t="inlineStr">
         <is>
-          <t>Registration Clerk</t>
+          <t>Mental Health Nurse</t>
         </is>
       </c>
       <c r="F5" s="799" t="inlineStr">
         <is>
-          <t>Patients &gt; Create: x; See patient file: blank</t>
+          <t>No « Edit sensitive mental health fields »</t>
         </is>
       </c>
       <c r="G5" s="799" t="inlineStr">
         <is>
-          <t>From the User roles and privileges tab</t>
+          <t>Today: difference, not locked in F31 (was in F03)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="799" t="inlineStr">
         <is>
-          <t>ROLES-2</t>
+          <t>ROLES-3</t>
         </is>
       </c>
       <c r="B6" s="799" t="inlineStr">
         <is>
-          <t>Open a patient file and try to order a lab test</t>
+          <t>Open the order basket, try to order a lab test</t>
         </is>
       </c>
       <c r="C6" s="799" t="inlineStr">
@@ -12285,235 +12295,147 @@
       </c>
       <c r="E6" s="799" t="inlineStr">
         <is>
-          <t>MH counselor</t>
+          <t>Mental Health Counselor (MH counselor)</t>
         </is>
       </c>
       <c r="F6" s="799" t="inlineStr">
         <is>
-          <t>Lab &gt; Order lab test: blank</t>
+          <t>Matrix: Order lab test blank</t>
         </is>
       </c>
       <c r="G6" s="799" t="inlineStr">
         <is>
-          <t>From the User roles and privileges tab</t>
+          <t>Today: difference, the EMR role can add orders</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="799" t="inlineStr">
         <is>
-          <t>ROLES-3</t>
+          <t>APPT-1</t>
         </is>
       </c>
       <c r="B7" s="799" t="inlineStr">
         <is>
-          <t>Open a patient file, go to Vitals</t>
+          <t>Book a follow-up appointment</t>
         </is>
       </c>
       <c r="C7" s="799" t="inlineStr">
         <is>
-          <t>Vitals are visible, no « Add » button</t>
+          <t>One service per counselor: Mental Health - AB, DT, KA, SA, SK</t>
         </is>
       </c>
       <c r="E7" s="799" t="inlineStr">
         <is>
-          <t>MedCo</t>
-        </is>
-      </c>
-      <c r="F7" s="799" t="inlineStr">
-        <is>
-          <t>Vitals &gt; View: x; Add: blank</t>
-        </is>
-      </c>
-      <c r="G7" s="799" t="inlineStr">
-        <is>
-          <t>From the User roles and privileges tab</t>
-        </is>
-      </c>
+          <t>Registration Officer</t>
+        </is>
+      </c>
+      <c r="F7" s="799" t="n"/>
+      <c r="G7" s="799" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="799" t="inlineStr">
         <is>
-          <t>ROLES-4</t>
+          <t>REG-1</t>
         </is>
       </c>
       <c r="B8" s="799" t="inlineStr">
         <is>
-          <t>Open a past visit and try to edit it</t>
+          <t>Register a new patient</t>
         </is>
       </c>
       <c r="C8" s="799" t="inlineStr">
         <is>
-          <t>Editing is refused</t>
+          <t>An MSF ID is generated automatically: prefix IQ146-, at most 16 characters</t>
         </is>
       </c>
       <c r="E8" s="799" t="inlineStr">
         <is>
-          <t>MH psychologist</t>
-        </is>
-      </c>
-      <c r="F8" s="799" t="inlineStr">
-        <is>
-          <t>Visits &gt; Edit: blank</t>
-        </is>
-      </c>
+          <t>Registration Officer</t>
+        </is>
+      </c>
+      <c r="F8" s="799" t="n"/>
       <c r="G8" s="799" t="inlineStr">
         <is>
-          <t>From the User roles and privileges tab</t>
+          <t>Today: config matches</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="799" t="inlineStr">
         <is>
-          <t>REG-1</t>
+          <t>VISIT-1</t>
         </is>
       </c>
       <c r="B9" s="799" t="inlineStr">
         <is>
-          <t>Register a new patient</t>
+          <t>Start a visit</t>
         </is>
       </c>
       <c r="C9" s="799" t="inlineStr">
         <is>
-          <t>An MSF ID is generated with the prefix IQ146- and at most 16 characters</t>
+          <t>Visit types offered: OPD Visit, ER Visit, IPD Visit, Telehealth</t>
         </is>
       </c>
       <c r="E9" s="799" t="inlineStr">
         <is>
-          <t>Registration Clerk</t>
+          <t>Mental Health Counselor</t>
         </is>
       </c>
       <c r="G9" s="799" t="inlineStr">
         <is>
-          <t>From the Patient Identifiers tab</t>
+          <t>Visit Types tab is out of date: update it first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="799" t="inlineStr">
         <is>
-          <t>PRINT-1</t>
+          <t>DHIS2-1</t>
         </is>
       </c>
       <c r="B10" s="799" t="inlineStr">
         <is>
-          <t>Print the patient sticker</t>
+          <t>Save an F35 PHQ-9, wait for the daily DHIS2 sync</t>
         </is>
       </c>
       <c r="C10" s="799" t="inlineStr">
         <is>
-          <t>Shows Patient ID, first and last name, gender and date of birth, in Arabic</t>
+          <t>The PHQ-9 score appears in DHIS2 for that patient</t>
         </is>
       </c>
       <c r="E10" s="799" t="inlineStr">
         <is>
-          <t>Registration Clerk</t>
-        </is>
-      </c>
-      <c r="G10" s="799" t="inlineStr">
-        <is>
-          <t>From the Patient Sticker tab</t>
-        </is>
-      </c>
+          <t>Automatic (daily sync)</t>
+        </is>
+      </c>
+      <c r="G10" s="799" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="799" t="inlineStr">
-        <is>
-          <t>APPT-1</t>
-        </is>
-      </c>
-      <c r="B11" s="799" t="inlineStr">
-        <is>
-          <t>Book an appointment for a patient</t>
-        </is>
-      </c>
-      <c r="C11" s="799" t="inlineStr">
-        <is>
-          <t>Services offered: Mental Health, and the Mental Health sub-services (AB, DT, KA, SA, SK)</t>
-        </is>
-      </c>
-      <c r="E11" s="799" t="inlineStr">
-        <is>
-          <t>MH psychologist</t>
-        </is>
-      </c>
-      <c r="G11" s="799" t="inlineStr">
-        <is>
-          <t>Appointment Service Definitions tab is out of date (lists General Medicine, OPD, Rehabilitation): update it first</t>
-        </is>
-      </c>
+      <c r="A11" s="799" t="n"/>
+      <c r="B11" s="799" t="n"/>
+      <c r="C11" s="799" t="n"/>
+      <c r="E11" s="799" t="n"/>
+      <c r="G11" s="799" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="799" t="inlineStr">
-        <is>
-          <t>VISIT-1</t>
-        </is>
-      </c>
-      <c r="B12" s="799" t="inlineStr">
-        <is>
-          <t>Start a visit</t>
-        </is>
-      </c>
-      <c r="C12" s="799" t="inlineStr">
-        <is>
-          <t>Visit types offered: OPD Visit, ER Visit, IPD Visit, Telehealth</t>
-        </is>
-      </c>
-      <c r="E12" s="799" t="inlineStr">
-        <is>
-          <t>MH psychologist</t>
-        </is>
-      </c>
-      <c r="G12" s="799" t="inlineStr">
-        <is>
-          <t>Visit Types tab is out of date (lists Facility, Home, Offline, Group Session visits): update it first</t>
-        </is>
-      </c>
+      <c r="A12" s="799" t="n"/>
+      <c r="B12" s="799" t="n"/>
+      <c r="C12" s="799" t="n"/>
+      <c r="E12" s="799" t="n"/>
+      <c r="G12" s="799" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="799" t="inlineStr">
-        <is>
-          <t>DHIS2-1</t>
-        </is>
-      </c>
-      <c r="B13" s="799" t="inlineStr">
-        <is>
-          <t>Save an F17 form, wait for the next DHIS2 sync</t>
-        </is>
-      </c>
-      <c r="C13" s="799" t="inlineStr">
-        <is>
-          <t>The admission appears in DHIS2 with the right date</t>
-        </is>
-      </c>
-      <c r="E13" s="799" t="inlineStr">
-        <is>
-          <t>Data officer</t>
-        </is>
-      </c>
+      <c r="A13" s="799" t="n"/>
+      <c r="B13" s="799" t="n"/>
+      <c r="C13" s="799" t="n"/>
+      <c r="E13" s="799" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="799" t="inlineStr">
-        <is>
-          <t>REPORT-1</t>
-        </is>
-      </c>
-      <c r="B14" s="799" t="inlineStr">
-        <is>
-          <t>Run the monthly mental health report for last month</t>
-        </is>
-      </c>
-      <c r="C14" s="799" t="inlineStr">
-        <is>
-          <t>The number of new patients matches the patient list</t>
-        </is>
-      </c>
-      <c r="E14" s="799" t="inlineStr">
-        <is>
-          <t>MH manager</t>
-        </is>
-      </c>
+      <c r="A14" s="799" t="n"/>
+      <c r="B14" s="799" t="n"/>
+      <c r="C14" s="799" t="n"/>
+      <c r="E14" s="799" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13185,6 +13107,7 @@
       <c r="C28" s="238" t="n"/>
       <c r="D28" s="238" t="n"/>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="800" t="inlineStr">
         <is>
@@ -13198,7 +13121,7 @@
       </c>
       <c r="C30" s="799" t="inlineStr">
         <is>
-          <t>Test: Enter 450 -&gt; A warning: the weight is not plausible</t>
+          <t>Test: Enter 450 -&gt; The value is refused (needs an Upper limit)</t>
         </is>
       </c>
       <c r="D30" s="799" t="inlineStr">

--- a/docs/testing/metadonnees/Template - Tests in metadata workbook.xlsx
+++ b/docs/testing/metadonnees/Template - Tests in metadata workbook.xlsx
@@ -8307,56 +8307,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>LIME</author>
-  </authors>
-  <commentList>
-    <comment ref="BK2" authorId="0" shapeId="0">
-      <text>
-        <t>Tests on this question go here, one per line: 'Test: &lt;what I do&gt; -&gt; &lt;what I should see&gt;'. Skip logic, Mandatory and limits already become tests automatically.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>LIME</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>Step = form code + step number (F17-1, F17-2...). Action = what I do. Description = what I should see. One scenario = the steps sharing the same prefix.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>LIME</author>
-  </authors>
-  <commentList>
-    <comment ref="B8" authorId="0" shapeId="0">
-      <text>
-        <t>From scripts/metadata-check.py --all: questions present, mandatory, limits.</t>
-      </text>
-    </comment>
-    <comment ref="D8" authorId="0" shapeId="0">
-      <text>
-        <t>From scripts/metadata-check.py --all: every Skip logic rule, both ways.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
@@ -11555,11 +11505,7 @@
       </c>
       <c r="BI14" s="665" t="n"/>
       <c r="BJ14" s="665" t="n"/>
-      <c r="BK14" s="799" t="inlineStr">
-        <is>
-          <t>Test: Enter 450 -&gt; The value is refused (needs an Upper limit)</t>
-        </is>
-      </c>
+      <c r="BK14" s="799" t="n"/>
       <c r="BN14" t="inlineStr">
         <is>
           <t>F17-Surgery admission form|9e3c4083-21bd-42d4-a2b5-657bc0b8a4a5</t>
@@ -12055,7 +12001,7 @@
       <c r="BJ17" s="670" t="n"/>
       <c r="BK17" s="799" t="inlineStr">
         <is>
-          <t>Test: Click « Order medications » -&gt; The order basket opens for this patient</t>
+          <t>Test: Click « Order medications » -&gt; The order basket opens</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -12105,7 +12051,6 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -12167,248 +12112,164 @@
     <row r="2">
       <c r="A2" s="799" t="inlineStr">
         <is>
-          <t>F31-1</t>
+          <t>ROLES-1</t>
         </is>
       </c>
       <c r="B2" s="799" t="inlineStr">
         <is>
-          <t>Save an F31 mhGAP Baseline during an active visit, then open the patient chart</t>
+          <t>Open the patient chart of a mental health patient</t>
         </is>
       </c>
       <c r="C2" s="799" t="inlineStr">
         <is>
-          <t>The form appears under the visit in the Visits tab and in Forms &amp; Notes</t>
-        </is>
-      </c>
-      <c r="D2" s="799" t="inlineStr">
-        <is>
-          <t>Fictitious patient, active visit</t>
-        </is>
-      </c>
+          <t>Mental health encounters are not visible</t>
+        </is>
+      </c>
+      <c r="D2" s="799" t="n"/>
       <c r="E2" s="799" t="inlineStr">
         <is>
-          <t>Mental Health Counselor (MH counselor)</t>
+          <t>Registration Officer (Registration Clerk)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="799" t="inlineStr">
         <is>
-          <t>F35-1</t>
+          <t>ROLES-2</t>
         </is>
       </c>
       <c r="B3" s="799" t="inlineStr">
         <is>
-          <t>Answer « Nearly every day (3 points) » to the 9 PHQ-9 questions</t>
+          <t>Open an F31 mhGAP Baseline, go to Clinical diagnosis</t>
         </is>
       </c>
       <c r="C3" s="799" t="inlineStr">
         <is>
-          <t>PHQ-9 score = 27</t>
+          <t>The section is read-only (no « Edit sensitive mental health fields » right)</t>
         </is>
       </c>
       <c r="E3" s="799" t="inlineStr">
         <is>
-          <t>Mental Health Counselor (MH counselor)</t>
+          <t>Mental Health Nurse</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="799" t="inlineStr">
         <is>
-          <t>ROLES-1</t>
+          <t>ROLES-3</t>
         </is>
       </c>
       <c r="B4" s="799" t="inlineStr">
         <is>
-          <t>Open the patient chart of a mental health patient</t>
+          <t>Try to order a lab test</t>
         </is>
       </c>
       <c r="C4" s="799" t="inlineStr">
         <is>
-          <t>Mental health forms are not visible</t>
+          <t>No lab order option (matrix: « Order lab test » blank)</t>
         </is>
       </c>
       <c r="E4" s="799" t="inlineStr">
         <is>
-          <t>Registration Officer (Registration Clerk)</t>
-        </is>
-      </c>
-      <c r="F4" s="799" t="inlineStr">
-        <is>
-          <t>No « View Mental Health »</t>
-        </is>
-      </c>
-      <c r="G4" s="799" t="inlineStr">
-        <is>
-          <t>Today: config matches</t>
-        </is>
-      </c>
+          <t>Mental Health Counselor (MH counselor)</t>
+        </is>
+      </c>
+      <c r="F4" s="799" t="n"/>
+      <c r="G4" s="799" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="799" t="inlineStr">
         <is>
-          <t>ROLES-2</t>
+          <t>APPT-1</t>
         </is>
       </c>
       <c r="B5" s="799" t="inlineStr">
         <is>
-          <t>Open an F31 mhGAP Baseline, go to Clinical diagnosis</t>
+          <t>Book a follow-up appointment</t>
         </is>
       </c>
       <c r="C5" s="799" t="inlineStr">
         <is>
-          <t>The section is read-only</t>
+          <t>Services: Mental Health, and Mental Health - AB, DT, KA, SA, SK</t>
         </is>
       </c>
       <c r="E5" s="799" t="inlineStr">
         <is>
-          <t>Mental Health Nurse</t>
-        </is>
-      </c>
-      <c r="F5" s="799" t="inlineStr">
-        <is>
-          <t>No « Edit sensitive mental health fields »</t>
-        </is>
-      </c>
-      <c r="G5" s="799" t="inlineStr">
-        <is>
-          <t>Today: difference, not locked in F31 (was in F03)</t>
-        </is>
-      </c>
+          <t>Mental Health Counselor</t>
+        </is>
+      </c>
+      <c r="F5" s="799" t="n"/>
+      <c r="G5" s="799" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="799" t="inlineStr">
         <is>
-          <t>ROLES-3</t>
+          <t>REG-1</t>
         </is>
       </c>
       <c r="B6" s="799" t="inlineStr">
         <is>
-          <t>Open the order basket, try to order a lab test</t>
+          <t>Register a new patient</t>
         </is>
       </c>
       <c r="C6" s="799" t="inlineStr">
         <is>
-          <t>No lab order option</t>
+          <t>An MSF ID is generated automatically: prefix IQ146-, at most 16 characters</t>
         </is>
       </c>
       <c r="E6" s="799" t="inlineStr">
         <is>
-          <t>Mental Health Counselor (MH counselor)</t>
-        </is>
-      </c>
-      <c r="F6" s="799" t="inlineStr">
-        <is>
-          <t>Matrix: Order lab test blank</t>
-        </is>
-      </c>
-      <c r="G6" s="799" t="inlineStr">
-        <is>
-          <t>Today: difference, the EMR role can add orders</t>
-        </is>
-      </c>
+          <t>Registration Officer</t>
+        </is>
+      </c>
+      <c r="F6" s="799" t="n"/>
+      <c r="G6" s="799" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="799" t="inlineStr">
         <is>
-          <t>APPT-1</t>
+          <t>DHIS2-1</t>
         </is>
       </c>
       <c r="B7" s="799" t="inlineStr">
         <is>
-          <t>Book a follow-up appointment</t>
+          <t>Save an F31 mhGAP Baseline with a PHQ-9 score</t>
         </is>
       </c>
       <c r="C7" s="799" t="inlineStr">
         <is>
-          <t>One service per counselor: Mental Health - AB, DT, KA, SA, SK</t>
+          <t>After the daily sync (17:00), the PHQ-9 score is in DHIS2</t>
         </is>
       </c>
       <c r="E7" s="799" t="inlineStr">
         <is>
-          <t>Registration Officer</t>
+          <t>Automatic</t>
         </is>
       </c>
       <c r="F7" s="799" t="n"/>
       <c r="G7" s="799" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="799" t="inlineStr">
-        <is>
-          <t>REG-1</t>
-        </is>
-      </c>
-      <c r="B8" s="799" t="inlineStr">
-        <is>
-          <t>Register a new patient</t>
-        </is>
-      </c>
-      <c r="C8" s="799" t="inlineStr">
-        <is>
-          <t>An MSF ID is generated automatically: prefix IQ146-, at most 16 characters</t>
-        </is>
-      </c>
-      <c r="E8" s="799" t="inlineStr">
-        <is>
-          <t>Registration Officer</t>
-        </is>
-      </c>
+      <c r="A8" s="799" t="n"/>
+      <c r="B8" s="799" t="n"/>
+      <c r="C8" s="799" t="n"/>
+      <c r="E8" s="799" t="n"/>
       <c r="F8" s="799" t="n"/>
-      <c r="G8" s="799" t="inlineStr">
-        <is>
-          <t>Today: config matches</t>
-        </is>
-      </c>
+      <c r="G8" s="799" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="799" t="inlineStr">
-        <is>
-          <t>VISIT-1</t>
-        </is>
-      </c>
-      <c r="B9" s="799" t="inlineStr">
-        <is>
-          <t>Start a visit</t>
-        </is>
-      </c>
-      <c r="C9" s="799" t="inlineStr">
-        <is>
-          <t>Visit types offered: OPD Visit, ER Visit, IPD Visit, Telehealth</t>
-        </is>
-      </c>
-      <c r="E9" s="799" t="inlineStr">
-        <is>
-          <t>Mental Health Counselor</t>
-        </is>
-      </c>
-      <c r="G9" s="799" t="inlineStr">
-        <is>
-          <t>Visit Types tab is out of date: update it first</t>
-        </is>
-      </c>
+      <c r="A9" s="799" t="n"/>
+      <c r="B9" s="799" t="n"/>
+      <c r="C9" s="799" t="n"/>
+      <c r="E9" s="799" t="n"/>
+      <c r="G9" s="799" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="799" t="inlineStr">
-        <is>
-          <t>DHIS2-1</t>
-        </is>
-      </c>
-      <c r="B10" s="799" t="inlineStr">
-        <is>
-          <t>Save an F35 PHQ-9, wait for the daily DHIS2 sync</t>
-        </is>
-      </c>
-      <c r="C10" s="799" t="inlineStr">
-        <is>
-          <t>The PHQ-9 score appears in DHIS2 for that patient</t>
-        </is>
-      </c>
-      <c r="E10" s="799" t="inlineStr">
-        <is>
-          <t>Automatic (daily sync)</t>
-        </is>
-      </c>
+      <c r="A10" s="799" t="n"/>
+      <c r="B10" s="799" t="n"/>
+      <c r="C10" s="799" t="n"/>
+      <c r="E10" s="799" t="n"/>
       <c r="G10" s="799" t="n"/>
     </row>
     <row r="11">
@@ -12439,7 +12300,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -12750,7 +12610,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -13116,17 +12975,17 @@
       </c>
       <c r="B30" s="799" t="inlineStr">
         <is>
-          <t>Skip logic, Mandatory and Lower/Upper limit become tests automatically. Other tests on a question: in 'Comments', one per line, 'Test: &lt;what I do&gt; -&gt; &lt;what I should see&gt;'. Tests across questions or forms: 'User flow template' tab (Action = what I do, Description = what I should see).</t>
+          <t>Other tests on a question: in 'Comments', 'Test: &lt;what I do&gt; -&gt; &lt;what I should see&gt;'. Tests across questions or forms: 'User flow template' (Action = what I do, Description = what I should see).</t>
         </is>
       </c>
       <c r="C30" s="799" t="inlineStr">
         <is>
-          <t>Test: Enter 450 -&gt; The value is refused (needs an Upper limit)</t>
+          <t>Test: Click « Order medications » -&gt; The order basket opens</t>
         </is>
       </c>
       <c r="D30" s="799" t="inlineStr">
         <is>
-          <t>Test: weight works</t>
+          <t>Test: button works</t>
         </is>
       </c>
     </row>

--- a/docs/testing/metadonnees/Template - Tests in metadata workbook.xlsx
+++ b/docs/testing/metadonnees/Template - Tests in metadata workbook.xlsx
@@ -12060,7 +12060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="14.45"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12112,67 +12112,67 @@
     <row r="2">
       <c r="A2" s="799" t="inlineStr">
         <is>
-          <t>ROLES-1</t>
+          <t>LOGIN-1</t>
         </is>
       </c>
       <c r="B2" s="799" t="inlineStr">
         <is>
-          <t>Open the patient chart of a mental health patient</t>
+          <t>Log in</t>
         </is>
       </c>
       <c r="C2" s="799" t="inlineStr">
         <is>
-          <t>Mental health encounters are not visible</t>
+          <t>Two locations offered: Mental Health (MH) / الصحة النفسية, and Registration Counter (REG) / تسجيل المستشفى</t>
         </is>
       </c>
       <c r="D2" s="799" t="n"/>
       <c r="E2" s="799" t="inlineStr">
         <is>
-          <t>Registration Officer (Registration Clerk)</t>
+          <t>Any user</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="799" t="inlineStr">
         <is>
-          <t>ROLES-2</t>
+          <t>LANG-1</t>
         </is>
       </c>
       <c r="B3" s="799" t="inlineStr">
         <is>
-          <t>Open an F31 mhGAP Baseline, go to Clinical diagnosis</t>
+          <t>Change the language</t>
         </is>
       </c>
       <c r="C3" s="799" t="inlineStr">
         <is>
-          <t>The section is read-only (no « Edit sensitive mental health fields » right)</t>
+          <t>English and Arabic offered; English by default</t>
         </is>
       </c>
       <c r="E3" s="799" t="inlineStr">
         <is>
-          <t>Mental Health Nurse</t>
+          <t>Any user</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="799" t="inlineStr">
         <is>
-          <t>ROLES-3</t>
+          <t>REG-1</t>
         </is>
       </c>
       <c r="B4" s="799" t="inlineStr">
         <is>
-          <t>Try to order a lab test</t>
+          <t>Register a new patient</t>
         </is>
       </c>
       <c r="C4" s="799" t="inlineStr">
         <is>
-          <t>No lab order option (matrix: « Order lab test » blank)</t>
+          <t>MSF ID generated automatically (prefix IQ146-, at most 16 characters); Legacy MSF ID optional</t>
         </is>
       </c>
       <c r="E4" s="799" t="inlineStr">
         <is>
-          <t>Mental Health Counselor (MH counselor)</t>
+          <t>Registration Officer</t>
         </is>
       </c>
       <c r="F4" s="799" t="n"/>
@@ -12181,22 +12181,22 @@
     <row r="5">
       <c r="A5" s="799" t="inlineStr">
         <is>
-          <t>APPT-1</t>
+          <t>REG-2</t>
         </is>
       </c>
       <c r="B5" s="799" t="inlineStr">
         <is>
-          <t>Book a follow-up appointment</t>
+          <t>Enter the patient address</t>
         </is>
       </c>
       <c r="C5" s="799" t="inlineStr">
         <is>
-          <t>Services: Mental Health, and Mental Health - AB, DT, KA, SA, SK</t>
+          <t>Address picked level by level: Iraq &gt; Ninawa &gt; district (Mosul, Sinjar, Talafar...) &gt; area</t>
         </is>
       </c>
       <c r="E5" s="799" t="inlineStr">
         <is>
-          <t>Mental Health Counselor</t>
+          <t>Registration Officer</t>
         </is>
       </c>
       <c r="F5" s="799" t="n"/>
@@ -12205,17 +12205,17 @@
     <row r="6">
       <c r="A6" s="799" t="inlineStr">
         <is>
-          <t>REG-1</t>
+          <t>REG-3</t>
         </is>
       </c>
       <c r="B6" s="799" t="inlineStr">
         <is>
-          <t>Register a new patient</t>
+          <t>Register a patient whose name is unknown</t>
         </is>
       </c>
       <c r="C6" s="799" t="inlineStr">
         <is>
-          <t>An MSF ID is generated automatically: prefix IQ146-, at most 16 characters</t>
+          <t>Registration is allowed</t>
         </is>
       </c>
       <c r="E6" s="799" t="inlineStr">
@@ -12229,74 +12229,208 @@
     <row r="7">
       <c r="A7" s="799" t="inlineStr">
         <is>
-          <t>DHIS2-1</t>
+          <t>REG-4</t>
         </is>
       </c>
       <c r="B7" s="799" t="inlineStr">
         <is>
-          <t>Save an F31 mhGAP Baseline with a PHQ-9 score</t>
+          <t>Open the patient chart</t>
         </is>
       </c>
       <c r="C7" s="799" t="inlineStr">
         <is>
-          <t>After the daily sync (17:00), the PHQ-9 score is in DHIS2</t>
+          <t>A « Print identifier sticker » button is available</t>
         </is>
       </c>
       <c r="E7" s="799" t="inlineStr">
         <is>
-          <t>Automatic</t>
+          <t>Registration Officer</t>
         </is>
       </c>
       <c r="F7" s="799" t="n"/>
       <c r="G7" s="799" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="799" t="n"/>
-      <c r="B8" s="799" t="n"/>
-      <c r="C8" s="799" t="n"/>
-      <c r="E8" s="799" t="n"/>
+      <c r="A8" s="799" t="inlineStr">
+        <is>
+          <t>ROLES-1</t>
+        </is>
+      </c>
+      <c r="B8" s="799" t="inlineStr">
+        <is>
+          <t>Open the patient chart of a mental health patient</t>
+        </is>
+      </c>
+      <c r="C8" s="799" t="inlineStr">
+        <is>
+          <t>Mental health encounters are not visible</t>
+        </is>
+      </c>
+      <c r="E8" s="799" t="inlineStr">
+        <is>
+          <t>Registration Officer</t>
+        </is>
+      </c>
       <c r="F8" s="799" t="n"/>
       <c r="G8" s="799" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="799" t="n"/>
-      <c r="B9" s="799" t="n"/>
-      <c r="C9" s="799" t="n"/>
-      <c r="E9" s="799" t="n"/>
+      <c r="A9" s="799" t="inlineStr">
+        <is>
+          <t>ROLES-2</t>
+        </is>
+      </c>
+      <c r="B9" s="799" t="inlineStr">
+        <is>
+          <t>Try to order a lab test</t>
+        </is>
+      </c>
+      <c r="C9" s="799" t="inlineStr">
+        <is>
+          <t>No lab order option</t>
+        </is>
+      </c>
+      <c r="E9" s="799" t="inlineStr">
+        <is>
+          <t>Mental Health Counselor</t>
+        </is>
+      </c>
       <c r="G9" s="799" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="799" t="n"/>
-      <c r="B10" s="799" t="n"/>
-      <c r="C10" s="799" t="n"/>
-      <c r="E10" s="799" t="n"/>
+      <c r="A10" s="799" t="inlineStr">
+        <is>
+          <t>APPT-1</t>
+        </is>
+      </c>
+      <c r="B10" s="799" t="inlineStr">
+        <is>
+          <t>Book a follow-up appointment</t>
+        </is>
+      </c>
+      <c r="C10" s="799" t="inlineStr">
+        <is>
+          <t>Services: Mental Health, and Mental Health - AB, DT, KA, SA, SK</t>
+        </is>
+      </c>
+      <c r="E10" s="799" t="inlineStr">
+        <is>
+          <t>Mental Health Counselor</t>
+        </is>
+      </c>
       <c r="G10" s="799" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="799" t="n"/>
-      <c r="B11" s="799" t="n"/>
-      <c r="C11" s="799" t="n"/>
-      <c r="E11" s="799" t="n"/>
+      <c r="A11" s="799" t="inlineStr">
+        <is>
+          <t>VISIT-1</t>
+        </is>
+      </c>
+      <c r="B11" s="799" t="inlineStr">
+        <is>
+          <t>Start a visit</t>
+        </is>
+      </c>
+      <c r="C11" s="799" t="inlineStr">
+        <is>
+          <t>Visit types offered: OPD Visit, ER Visit, IPD Visit, Telehealth</t>
+        </is>
+      </c>
+      <c r="E11" s="799" t="inlineStr">
+        <is>
+          <t>Mental Health Counselor</t>
+        </is>
+      </c>
       <c r="G11" s="799" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="799" t="n"/>
-      <c r="B12" s="799" t="n"/>
-      <c r="C12" s="799" t="n"/>
-      <c r="E12" s="799" t="n"/>
+      <c r="A12" s="799" t="inlineStr">
+        <is>
+          <t>VISIT-2</t>
+        </is>
+      </c>
+      <c r="B12" s="799" t="inlineStr">
+        <is>
+          <t>Leave an OPD or Telehealth visit open</t>
+        </is>
+      </c>
+      <c r="C12" s="799" t="inlineStr">
+        <is>
+          <t>The visit is closed automatically</t>
+        </is>
+      </c>
+      <c r="E12" s="799" t="inlineStr">
+        <is>
+          <t>Automatic</t>
+        </is>
+      </c>
       <c r="G12" s="799" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="799" t="n"/>
-      <c r="B13" s="799" t="n"/>
-      <c r="C13" s="799" t="n"/>
-      <c r="E13" s="799" t="n"/>
+      <c r="A13" s="799" t="inlineStr">
+        <is>
+          <t>EDIT-1</t>
+        </is>
+      </c>
+      <c r="B13" s="799" t="inlineStr">
+        <is>
+          <t>Edit a form saved more than 24 hours ago</t>
+        </is>
+      </c>
+      <c r="C13" s="799" t="inlineStr">
+        <is>
+          <t>The form can no longer be edited</t>
+        </is>
+      </c>
+      <c r="E13" s="799" t="inlineStr">
+        <is>
+          <t>Mental Health Counselor</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="799" t="n"/>
-      <c r="B14" s="799" t="n"/>
-      <c r="C14" s="799" t="n"/>
-      <c r="E14" s="799" t="n"/>
+      <c r="A14" s="799" t="inlineStr">
+        <is>
+          <t>RDE-1</t>
+        </is>
+      </c>
+      <c r="B14" s="799" t="inlineStr">
+        <is>
+          <t>Enter data for a past visit</t>
+        </is>
+      </c>
+      <c r="C14" s="799" t="inlineStr">
+        <is>
+          <t>Retrospective data entry is available</t>
+        </is>
+      </c>
+      <c r="E14" s="799" t="inlineStr">
+        <is>
+          <t>Mental Health Counselor</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="799" t="inlineStr">
+        <is>
+          <t>DHIS2-1</t>
+        </is>
+      </c>
+      <c r="B15" s="799" t="inlineStr">
+        <is>
+          <t>Save an F31 mhGAP Baseline with a PHQ-9 score</t>
+        </is>
+      </c>
+      <c r="C15" s="799" t="inlineStr">
+        <is>
+          <t>After the daily sync (17:00), the PHQ-9 score is in DHIS2</t>
+        </is>
+      </c>
+      <c r="E15" s="799" t="inlineStr">
+        <is>
+          <t>Automatic</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12966,7 +13100,6 @@
       <c r="C28" s="238" t="n"/>
       <c r="D28" s="238" t="n"/>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="800" t="inlineStr">
         <is>

--- a/docs/testing/metadonnees/Template - Tests in metadata workbook.xlsx
+++ b/docs/testing/metadonnees/Template - Tests in metadata workbook.xlsx
@@ -7,12 +7,13 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F17-Surgery Admission" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User flow template" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User flow template" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form QA Tracker" sheetId="3" state="hidden" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form Guidance" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'F17-Surgery Admission'!$A$2:$BP$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'User flow template'!$A$1:$M$1000</definedName>
   </definedNames>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
 </workbook>
@@ -25,7 +26,7 @@
     <numFmt numFmtId="165" formatCode="[$-2000401]0"/>
     <numFmt numFmtId="166" formatCode="[$-2000000]\d\d\-mmm"/>
   </numFmts>
-  <fonts count="129">
+  <fonts count="130">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -882,6 +883,12 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="FF2E75B6"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="63">
@@ -2101,7 +2108,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="801">
+  <cellXfs count="803">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3703,6 +3710,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="128" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3710,7 +3723,7 @@
     <cellStyle name="Normal 2" xfId="2"/>
     <cellStyle name="Normal 4" xfId="3"/>
   </cellStyles>
-  <dxfs count="518">
+  <dxfs count="521">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -8298,6 +8311,27 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="9" tint="0.7999816888943144"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -12056,384 +12090,966 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr codeName="Sheet24">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="14.45"/>
+  <dimension ref="A1:M17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="4"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="7"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26.25" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="801" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="801" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="C1" s="801" t="inlineStr">
+        <is>
+          <t>Site</t>
+        </is>
+      </c>
+      <c r="D1" s="801" t="inlineStr">
+        <is>
+          <t>Release</t>
+        </is>
+      </c>
+      <c r="E1" s="801" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="F1" s="801" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="G1" s="801" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="H1" s="801" t="inlineStr">
         <is>
           <t>User</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="I1" s="801" t="inlineStr">
         <is>
           <t>Permission</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="J1" s="801" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="K1" s="801" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="L1" s="801" t="inlineStr">
+        <is>
+          <t>Tested on</t>
+        </is>
+      </c>
+      <c r="M1" s="801" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="799" t="inlineStr">
+      <c r="A2" s="802" t="inlineStr">
         <is>
           <t>LOGIN-1</t>
         </is>
       </c>
-      <c r="B2" s="799" t="inlineStr">
+      <c r="B2" s="802" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="C2" s="802" t="inlineStr">
+        <is>
+          <t>Mosul</t>
+        </is>
+      </c>
+      <c r="D2" s="802" t="inlineStr">
+        <is>
+          <t>Release 1</t>
+        </is>
+      </c>
+      <c r="E2" s="802" t="inlineStr">
         <is>
           <t>Log in</t>
         </is>
       </c>
-      <c r="C2" s="799" t="inlineStr">
+      <c r="F2" s="802" t="inlineStr">
         <is>
           <t>Two locations offered: Mental Health (MH) / الصحة النفسية, and Registration Counter (REG) / تسجيل المستشفى</t>
         </is>
       </c>
-      <c r="D2" s="799" t="n"/>
-      <c r="E2" s="799" t="inlineStr">
+      <c r="G2" s="802" t="n"/>
+      <c r="H2" s="802" t="inlineStr">
         <is>
           <t>Any user</t>
         </is>
       </c>
+      <c r="I2" s="802" t="n"/>
+      <c r="J2" s="802" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K2" s="802" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L2" s="802" t="n"/>
+      <c r="M2" s="802" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="799" t="inlineStr">
+      <c r="A3" s="802" t="inlineStr">
         <is>
           <t>LANG-1</t>
         </is>
       </c>
-      <c r="B3" s="799" t="inlineStr">
+      <c r="B3" s="802" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C3" s="802" t="inlineStr">
+        <is>
+          <t>Mosul</t>
+        </is>
+      </c>
+      <c r="D3" s="802" t="inlineStr">
+        <is>
+          <t>Release 1</t>
+        </is>
+      </c>
+      <c r="E3" s="802" t="inlineStr">
         <is>
           <t>Change the language</t>
         </is>
       </c>
-      <c r="C3" s="799" t="inlineStr">
+      <c r="F3" s="802" t="inlineStr">
         <is>
           <t>English and Arabic offered; English by default</t>
         </is>
       </c>
-      <c r="E3" s="799" t="inlineStr">
+      <c r="G3" s="802" t="n"/>
+      <c r="H3" s="802" t="inlineStr">
         <is>
           <t>Any user</t>
         </is>
       </c>
+      <c r="I3" s="802" t="n"/>
+      <c r="J3" s="802" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="K3" s="802" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L3" s="802" t="n"/>
+      <c r="M3" s="802" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="799" t="inlineStr">
+      <c r="A4" s="802" t="inlineStr">
         <is>
           <t>REG-1</t>
         </is>
       </c>
-      <c r="B4" s="799" t="inlineStr">
+      <c r="B4" s="802" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C4" s="802" t="inlineStr">
+        <is>
+          <t>Mosul</t>
+        </is>
+      </c>
+      <c r="D4" s="802" t="inlineStr">
+        <is>
+          <t>Release 1</t>
+        </is>
+      </c>
+      <c r="E4" s="802" t="inlineStr">
         <is>
           <t>Register a new patient</t>
         </is>
       </c>
-      <c r="C4" s="799" t="inlineStr">
+      <c r="F4" s="802" t="inlineStr">
         <is>
           <t>MSF ID generated automatically (prefix IQ146-, at most 16 characters); Legacy MSF ID optional</t>
         </is>
       </c>
-      <c r="E4" s="799" t="inlineStr">
+      <c r="G4" s="802" t="inlineStr">
+        <is>
+          <t>Fictitious patient</t>
+        </is>
+      </c>
+      <c r="H4" s="802" t="inlineStr">
         <is>
           <t>Registration Officer</t>
         </is>
       </c>
-      <c r="F4" s="799" t="n"/>
-      <c r="G4" s="799" t="n"/>
+      <c r="I4" s="802" t="n"/>
+      <c r="J4" s="802" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K4" s="802" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L4" s="802" t="n"/>
+      <c r="M4" s="802" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="799" t="inlineStr">
+      <c r="A5" s="802" t="inlineStr">
         <is>
           <t>REG-2</t>
         </is>
       </c>
-      <c r="B5" s="799" t="inlineStr">
+      <c r="B5" s="802" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C5" s="802" t="inlineStr">
+        <is>
+          <t>Mosul</t>
+        </is>
+      </c>
+      <c r="D5" s="802" t="inlineStr">
+        <is>
+          <t>Release 1</t>
+        </is>
+      </c>
+      <c r="E5" s="802" t="inlineStr">
         <is>
           <t>Enter the patient address</t>
         </is>
       </c>
-      <c r="C5" s="799" t="inlineStr">
+      <c r="F5" s="802" t="inlineStr">
         <is>
           <t>Address picked level by level: Iraq &gt; Ninawa &gt; district (Mosul, Sinjar, Talafar...) &gt; area</t>
         </is>
       </c>
-      <c r="E5" s="799" t="inlineStr">
+      <c r="G5" s="802" t="n"/>
+      <c r="H5" s="802" t="inlineStr">
         <is>
           <t>Registration Officer</t>
         </is>
       </c>
-      <c r="F5" s="799" t="n"/>
-      <c r="G5" s="799" t="n"/>
+      <c r="I5" s="802" t="n"/>
+      <c r="J5" s="802" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="K5" s="802" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L5" s="802" t="n"/>
+      <c r="M5" s="802" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="799" t="inlineStr">
+      <c r="A6" s="802" t="inlineStr">
         <is>
           <t>REG-3</t>
         </is>
       </c>
-      <c r="B6" s="799" t="inlineStr">
+      <c r="B6" s="802" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C6" s="802" t="inlineStr">
+        <is>
+          <t>Mosul</t>
+        </is>
+      </c>
+      <c r="D6" s="802" t="inlineStr">
+        <is>
+          <t>Release 1</t>
+        </is>
+      </c>
+      <c r="E6" s="802" t="inlineStr">
         <is>
           <t>Register a patient whose name is unknown</t>
         </is>
       </c>
-      <c r="C6" s="799" t="inlineStr">
+      <c r="F6" s="802" t="inlineStr">
         <is>
           <t>Registration is allowed</t>
         </is>
       </c>
-      <c r="E6" s="799" t="inlineStr">
+      <c r="G6" s="802" t="n"/>
+      <c r="H6" s="802" t="inlineStr">
         <is>
           <t>Registration Officer</t>
         </is>
       </c>
-      <c r="F6" s="799" t="n"/>
-      <c r="G6" s="799" t="n"/>
+      <c r="I6" s="802" t="n"/>
+      <c r="J6" s="802" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="K6" s="802" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L6" s="802" t="n"/>
+      <c r="M6" s="802" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="799" t="inlineStr">
+      <c r="A7" s="802" t="inlineStr">
         <is>
           <t>REG-4</t>
         </is>
       </c>
-      <c r="B7" s="799" t="inlineStr">
+      <c r="B7" s="802" t="inlineStr">
+        <is>
+          <t>Printing</t>
+        </is>
+      </c>
+      <c r="C7" s="802" t="inlineStr">
+        <is>
+          <t>Mosul</t>
+        </is>
+      </c>
+      <c r="D7" s="802" t="inlineStr">
+        <is>
+          <t>Release 1</t>
+        </is>
+      </c>
+      <c r="E7" s="802" t="inlineStr">
         <is>
           <t>Open the patient chart</t>
         </is>
       </c>
-      <c r="C7" s="799" t="inlineStr">
+      <c r="F7" s="802" t="inlineStr">
         <is>
           <t>A « Print identifier sticker » button is available</t>
         </is>
       </c>
-      <c r="E7" s="799" t="inlineStr">
+      <c r="G7" s="802" t="n"/>
+      <c r="H7" s="802" t="inlineStr">
         <is>
           <t>Registration Officer</t>
         </is>
       </c>
-      <c r="F7" s="799" t="n"/>
-      <c r="G7" s="799" t="n"/>
+      <c r="I7" s="802" t="n"/>
+      <c r="J7" s="802" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="K7" s="802" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L7" s="802" t="n"/>
+      <c r="M7" s="802" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="799" t="inlineStr">
+      <c r="A8" s="802" t="inlineStr">
         <is>
           <t>ROLES-1</t>
         </is>
       </c>
-      <c r="B8" s="799" t="inlineStr">
+      <c r="B8" s="802" t="inlineStr">
+        <is>
+          <t>Access and roles</t>
+        </is>
+      </c>
+      <c r="C8" s="802" t="inlineStr">
+        <is>
+          <t>Mosul</t>
+        </is>
+      </c>
+      <c r="D8" s="802" t="inlineStr">
+        <is>
+          <t>Release 1</t>
+        </is>
+      </c>
+      <c r="E8" s="802" t="inlineStr">
         <is>
           <t>Open the patient chart of a mental health patient</t>
         </is>
       </c>
-      <c r="C8" s="799" t="inlineStr">
+      <c r="F8" s="802" t="inlineStr">
         <is>
           <t>Mental health encounters are not visible</t>
         </is>
       </c>
-      <c r="E8" s="799" t="inlineStr">
+      <c r="G8" s="802" t="n"/>
+      <c r="H8" s="802" t="inlineStr">
         <is>
           <t>Registration Officer</t>
         </is>
       </c>
-      <c r="F8" s="799" t="n"/>
-      <c r="G8" s="799" t="n"/>
+      <c r="I8" s="802" t="inlineStr">
+        <is>
+          <t>No « View Mental Health »</t>
+        </is>
+      </c>
+      <c r="J8" s="802" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K8" s="802" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L8" s="802" t="n"/>
+      <c r="M8" s="802" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="799" t="inlineStr">
+      <c r="A9" s="802" t="inlineStr">
         <is>
           <t>ROLES-2</t>
         </is>
       </c>
-      <c r="B9" s="799" t="inlineStr">
+      <c r="B9" s="802" t="inlineStr">
+        <is>
+          <t>Access and roles</t>
+        </is>
+      </c>
+      <c r="C9" s="802" t="inlineStr">
+        <is>
+          <t>Mosul</t>
+        </is>
+      </c>
+      <c r="D9" s="802" t="inlineStr">
+        <is>
+          <t>Release 1</t>
+        </is>
+      </c>
+      <c r="E9" s="802" t="inlineStr">
         <is>
           <t>Try to order a lab test</t>
         </is>
       </c>
-      <c r="C9" s="799" t="inlineStr">
+      <c r="F9" s="802" t="inlineStr">
         <is>
           <t>No lab order option</t>
         </is>
       </c>
-      <c r="E9" s="799" t="inlineStr">
+      <c r="G9" s="802" t="n"/>
+      <c r="H9" s="802" t="inlineStr">
         <is>
           <t>Mental Health Counselor</t>
         </is>
       </c>
-      <c r="G9" s="799" t="n"/>
+      <c r="I9" s="802" t="inlineStr">
+        <is>
+          <t>Matrix: « Order lab test » blank</t>
+        </is>
+      </c>
+      <c r="J9" s="802" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="K9" s="802" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L9" s="802" t="n"/>
+      <c r="M9" s="802" t="inlineStr">
+        <is>
+          <t>Today the EMR role can add orders</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="799" t="inlineStr">
+      <c r="A10" s="802" t="inlineStr">
         <is>
           <t>APPT-1</t>
         </is>
       </c>
-      <c r="B10" s="799" t="inlineStr">
+      <c r="B10" s="802" t="inlineStr">
+        <is>
+          <t>Appointments</t>
+        </is>
+      </c>
+      <c r="C10" s="802" t="inlineStr">
+        <is>
+          <t>Mosul</t>
+        </is>
+      </c>
+      <c r="D10" s="802" t="inlineStr">
+        <is>
+          <t>Release 1</t>
+        </is>
+      </c>
+      <c r="E10" s="802" t="inlineStr">
         <is>
           <t>Book a follow-up appointment</t>
         </is>
       </c>
-      <c r="C10" s="799" t="inlineStr">
+      <c r="F10" s="802" t="inlineStr">
         <is>
           <t>Services: Mental Health, and Mental Health - AB, DT, KA, SA, SK</t>
         </is>
       </c>
-      <c r="E10" s="799" t="inlineStr">
+      <c r="G10" s="802" t="n"/>
+      <c r="H10" s="802" t="inlineStr">
         <is>
           <t>Mental Health Counselor</t>
         </is>
       </c>
-      <c r="G10" s="799" t="n"/>
+      <c r="I10" s="802" t="n"/>
+      <c r="J10" s="802" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="K10" s="802" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L10" s="802" t="n"/>
+      <c r="M10" s="802" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="799" t="inlineStr">
+      <c r="A11" s="802" t="inlineStr">
         <is>
           <t>VISIT-1</t>
         </is>
       </c>
-      <c r="B11" s="799" t="inlineStr">
+      <c r="B11" s="802" t="inlineStr">
+        <is>
+          <t>Visits</t>
+        </is>
+      </c>
+      <c r="C11" s="802" t="inlineStr">
+        <is>
+          <t>Mosul</t>
+        </is>
+      </c>
+      <c r="D11" s="802" t="inlineStr">
+        <is>
+          <t>Release 1</t>
+        </is>
+      </c>
+      <c r="E11" s="802" t="inlineStr">
         <is>
           <t>Start a visit</t>
         </is>
       </c>
-      <c r="C11" s="799" t="inlineStr">
+      <c r="F11" s="802" t="inlineStr">
         <is>
           <t>Visit types offered: OPD Visit, ER Visit, IPD Visit, Telehealth</t>
         </is>
       </c>
-      <c r="E11" s="799" t="inlineStr">
+      <c r="G11" s="802" t="n"/>
+      <c r="H11" s="802" t="inlineStr">
         <is>
           <t>Mental Health Counselor</t>
         </is>
       </c>
-      <c r="G11" s="799" t="n"/>
+      <c r="I11" s="802" t="n"/>
+      <c r="J11" s="802" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="K11" s="802" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L11" s="802" t="n"/>
+      <c r="M11" s="802" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="799" t="inlineStr">
+      <c r="A12" s="802" t="inlineStr">
         <is>
           <t>VISIT-2</t>
         </is>
       </c>
-      <c r="B12" s="799" t="inlineStr">
+      <c r="B12" s="802" t="inlineStr">
+        <is>
+          <t>Visits</t>
+        </is>
+      </c>
+      <c r="C12" s="802" t="inlineStr">
+        <is>
+          <t>Mosul</t>
+        </is>
+      </c>
+      <c r="D12" s="802" t="inlineStr">
+        <is>
+          <t>Release 1</t>
+        </is>
+      </c>
+      <c r="E12" s="802" t="inlineStr">
         <is>
           <t>Leave an OPD or Telehealth visit open</t>
         </is>
       </c>
-      <c r="C12" s="799" t="inlineStr">
+      <c r="F12" s="802" t="inlineStr">
         <is>
           <t>The visit is closed automatically</t>
         </is>
       </c>
-      <c r="E12" s="799" t="inlineStr">
+      <c r="G12" s="802" t="n"/>
+      <c r="H12" s="802" t="inlineStr">
         <is>
           <t>Automatic</t>
         </is>
       </c>
-      <c r="G12" s="799" t="n"/>
+      <c r="I12" s="802" t="n"/>
+      <c r="J12" s="802" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="K12" s="802" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L12" s="802" t="n"/>
+      <c r="M12" s="802" t="inlineStr">
+        <is>
+          <t>Auto-close list also names « Home Visit », not a Mosul visit type</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="799" t="inlineStr">
+      <c r="A13" s="802" t="inlineStr">
         <is>
           <t>EDIT-1</t>
         </is>
       </c>
-      <c r="B13" s="799" t="inlineStr">
+      <c r="B13" s="802" t="inlineStr">
+        <is>
+          <t>Patient chart</t>
+        </is>
+      </c>
+      <c r="C13" s="802" t="inlineStr">
+        <is>
+          <t>Mosul</t>
+        </is>
+      </c>
+      <c r="D13" s="802" t="inlineStr">
+        <is>
+          <t>Release 1</t>
+        </is>
+      </c>
+      <c r="E13" s="802" t="inlineStr">
         <is>
           <t>Edit a form saved more than 24 hours ago</t>
         </is>
       </c>
-      <c r="C13" s="799" t="inlineStr">
+      <c r="F13" s="802" t="inlineStr">
         <is>
           <t>The form can no longer be edited</t>
         </is>
       </c>
-      <c r="E13" s="799" t="inlineStr">
+      <c r="G13" s="802" t="n"/>
+      <c r="H13" s="802" t="inlineStr">
         <is>
           <t>Mental Health Counselor</t>
         </is>
       </c>
+      <c r="I13" s="802" t="n"/>
+      <c r="J13" s="802" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="K13" s="802" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L13" s="802" t="n"/>
+      <c r="M13" s="802" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="799" t="inlineStr">
+      <c r="A14" s="802" t="inlineStr">
         <is>
           <t>RDE-1</t>
         </is>
       </c>
-      <c r="B14" s="799" t="inlineStr">
+      <c r="B14" s="802" t="inlineStr">
+        <is>
+          <t>Patient chart</t>
+        </is>
+      </c>
+      <c r="C14" s="802" t="inlineStr">
+        <is>
+          <t>Mosul</t>
+        </is>
+      </c>
+      <c r="D14" s="802" t="inlineStr">
+        <is>
+          <t>Release 1</t>
+        </is>
+      </c>
+      <c r="E14" s="802" t="inlineStr">
         <is>
           <t>Enter data for a past visit</t>
         </is>
       </c>
-      <c r="C14" s="799" t="inlineStr">
+      <c r="F14" s="802" t="inlineStr">
         <is>
           <t>Retrospective data entry is available</t>
         </is>
       </c>
-      <c r="E14" s="799" t="inlineStr">
+      <c r="G14" s="802" t="n"/>
+      <c r="H14" s="802" t="inlineStr">
         <is>
           <t>Mental Health Counselor</t>
         </is>
       </c>
+      <c r="I14" s="802" t="n"/>
+      <c r="J14" s="802" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="K14" s="802" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L14" s="802" t="n"/>
+      <c r="M14" s="802" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="799" t="inlineStr">
+      <c r="A15" s="802" t="inlineStr">
         <is>
           <t>DHIS2-1</t>
         </is>
       </c>
-      <c r="B15" s="799" t="inlineStr">
+      <c r="B15" s="802" t="inlineStr">
+        <is>
+          <t>DHIS2 and OpenFn</t>
+        </is>
+      </c>
+      <c r="C15" s="802" t="inlineStr">
+        <is>
+          <t>Mosul</t>
+        </is>
+      </c>
+      <c r="D15" s="802" t="inlineStr">
+        <is>
+          <t>Release 1</t>
+        </is>
+      </c>
+      <c r="E15" s="802" t="inlineStr">
         <is>
           <t>Save an F31 mhGAP Baseline with a PHQ-9 score</t>
         </is>
       </c>
-      <c r="C15" s="799" t="inlineStr">
+      <c r="F15" s="802" t="inlineStr">
         <is>
           <t>After the daily sync (17:00), the PHQ-9 score is in DHIS2</t>
         </is>
       </c>
-      <c r="E15" s="799" t="inlineStr">
+      <c r="G15" s="802" t="n"/>
+      <c r="H15" s="802" t="inlineStr">
         <is>
           <t>Automatic</t>
         </is>
       </c>
+      <c r="I15" s="802" t="n"/>
+      <c r="J15" s="802" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K15" s="802" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L15" s="802" t="n"/>
+      <c r="M15" s="802" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="802" t="inlineStr">
+        <is>
+          <t>ROLES-1</t>
+        </is>
+      </c>
+      <c r="B16" s="802" t="inlineStr">
+        <is>
+          <t>Access and roles</t>
+        </is>
+      </c>
+      <c r="C16" s="802" t="inlineStr">
+        <is>
+          <t>Matsapha</t>
+        </is>
+      </c>
+      <c r="D16" s="802" t="n"/>
+      <c r="E16" s="802" t="inlineStr">
+        <is>
+          <t>Delete an encounter of a patient</t>
+        </is>
+      </c>
+      <c r="F16" s="802" t="inlineStr">
+        <is>
+          <t>Deletion works</t>
+        </is>
+      </c>
+      <c r="G16" s="802" t="inlineStr">
+        <is>
+          <t>Fictitious patient</t>
+        </is>
+      </c>
+      <c r="H16" s="802" t="inlineStr">
+        <is>
+          <t>Matsapha: Registration Supervisor</t>
+        </is>
+      </c>
+      <c r="I16" s="802" t="inlineStr">
+        <is>
+          <t>Delete Encounters</t>
+        </is>
+      </c>
+      <c r="J16" s="802" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K16" s="802" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L16" s="802" t="n"/>
+      <c r="M16" s="802" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="802" t="inlineStr">
+        <is>
+          <t>ROLES-2</t>
+        </is>
+      </c>
+      <c r="B17" s="802" t="inlineStr">
+        <is>
+          <t>Access and roles</t>
+        </is>
+      </c>
+      <c r="C17" s="802" t="inlineStr">
+        <is>
+          <t>Matsapha</t>
+        </is>
+      </c>
+      <c r="D17" s="802" t="n"/>
+      <c r="E17" s="802" t="inlineStr">
+        <is>
+          <t>Open the same patient and look for « Delete »</t>
+        </is>
+      </c>
+      <c r="F17" s="802" t="inlineStr">
+        <is>
+          <t>No delete option</t>
+        </is>
+      </c>
+      <c r="G17" s="802" t="n"/>
+      <c r="H17" s="802" t="inlineStr">
+        <is>
+          <t>Matsapha: Clinical</t>
+        </is>
+      </c>
+      <c r="I17" s="802" t="inlineStr">
+        <is>
+          <t>No Delete Encounters</t>
+        </is>
+      </c>
+      <c r="J17" s="802" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K17" s="802" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L17" s="802" t="n"/>
+      <c r="M17" s="802" t="n"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <autoFilter ref="A1:M1000"/>
+  <conditionalFormatting sqref="K2:K1000">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="518">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="519">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="520">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="5">
+    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Login,Language,Registration,Access and roles,Appointments,Visits,Patient chart,Forms,Orders and lab,DHIS2 and OpenFn,Reports,Printing,Offline"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"All sites,Mosul,Matsapha,Bunia"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Release 1,Release 2,Release 3"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Critical,Normal"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Not run,Pass,Fail,Blocked"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -13100,6 +13716,7 @@
       <c r="C28" s="238" t="n"/>
       <c r="D28" s="238" t="n"/>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="800" t="inlineStr">
         <is>
@@ -13108,7 +13725,7 @@
       </c>
       <c r="B30" s="799" t="inlineStr">
         <is>
-          <t>Other tests on a question: in 'Comments', 'Test: &lt;what I do&gt; -&gt; &lt;what I should see&gt;'. Tests across questions or forms: 'User flow template' (Action = what I do, Description = what I should see).</t>
+          <t>Other tests on a question: in 'Comments', 'Test: &lt;what I do&gt; -&gt; &lt;what I should see&gt;'. Tests across questions, forms or sites: one row in 'User flow template'. Site = All sites or one site; Release = phase; Result and Tested on are filled when the test is run.</t>
         </is>
       </c>
       <c r="C30" s="799" t="inlineStr">
